--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(4).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(4).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19275" windowHeight="10320"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线4层（终）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="481">
   <si>
     <t>ID</t>
   </si>
@@ -100,6 +100,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -254,6 +259,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -451,6 +461,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>老师，为什么一定要这样，这不是他们的错，你明明知道这一点</t>
     </r>
     <r>
@@ -655,7 +670,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>终局（上）</t>
+      <t>sntzm_final(3)</t>
     </r>
     <r>
       <rPr>
@@ -663,7 +678,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>_1, 1)</t>
+      <t>, 8))</t>
     </r>
   </si>
   <si>
@@ -748,7 +763,25 @@
     <t>随着又一重真相的揭示，这个被捆缚在椅子上的罪人形象，在你眼中顿时变得生动而真实，因为就连他这个始作俑者也不过是受困于意义之网的另一名可悲的囚徒。</t>
   </si>
   <si>
-    <t>loadScript(终局（上）_1, 1)</t>
+    <r>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_final(3)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, 8)</t>
+    </r>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=23; gotomainline=终局（上）_1</t>
@@ -1036,6 +1069,27 @@
     <t>屏幕上浮现出几行字，格式严谨，措辞冷淡，像一份被反复打磨过的商业提案，与项目充满宗教色彩的标题有些格格不入：</t>
   </si>
   <si>
+    <r>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_final(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, 1)</t>
+    </r>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=34</t>
   </si>
   <si>
@@ -1055,6 +1109,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -4672,7 +4731,6 @@
       <c r="J50" t="s">
         <v>15</v>
       </c>
-      <c r="K50"/>
       <c r="L50" t="s">
         <v>162</v>
       </c>
@@ -5202,7 +5260,7 @@
       <c r="J64" t="s">
         <v>15</v>
       </c>
-      <c r="K64" t="s">
+      <c r="K64" s="3" t="s">
         <v>200</v>
       </c>
       <c r="L64" t="s">
@@ -6494,16 +6552,16 @@
       <c r="J98" t="s">
         <v>15</v>
       </c>
-      <c r="K98" t="s">
-        <v>200</v>
+      <c r="K98" s="3" t="s">
+        <v>296</v>
       </c>
       <c r="L98" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="99" ht="150" spans="1:12">
       <c r="A99" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6521,7 +6579,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6536,12 +6594,12 @@
         <v>15</v>
       </c>
       <c r="L99" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="100" ht="40.5" spans="1:12">
       <c r="A100" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B100" t="s">
         <v>32</v>
@@ -6559,7 +6617,7 @@
         <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H100" t="s">
         <v>15</v>
@@ -6571,10 +6629,10 @@
         <v>15</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L100" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -6595,31 +6653,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B4" t="s">
         <v>190</v>
@@ -6627,7 +6685,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6635,15 +6693,15 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
@@ -6651,7 +6709,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -6659,7 +6717,7 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B9" t="s">
         <v>236</v>
@@ -6667,50 +6725,50 @@
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -6732,616 +6790,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E12" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B13" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D13" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E13" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B15" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C15" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D15" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F15" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B16" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C16" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D16" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E16" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F16" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B17" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C17" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E17" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F17" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B18" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D18" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E18" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F18" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B19" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C19" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D19" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E19" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F19" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B20" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C20" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D20" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E20" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F20" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B21" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C21" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D21" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F21" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B22" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C22" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D22" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E22" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F22" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B23" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C23" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D23" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E23" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F23" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B24" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C24" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D24" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E24" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F24" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B25" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C25" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D25" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E25" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F25" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C26" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D26" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E26" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F26" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B27" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C27" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D27" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E27" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F27" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B28" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C28" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D28" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E28" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F28" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B29" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C29" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D29" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E29" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F29" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B30" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C30" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D30" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E30" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F30" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B31" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C31" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D31" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
